--- a/output/pdf_financials_xlsx/BECN.xlsx
+++ b/output/pdf_financials_xlsx/BECN.xlsx
@@ -2196,13 +2196,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.308547</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.949568</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.24003</v>
       </c>
     </row>
     <row r="93">
@@ -2404,7 +2404,7 @@
         <v>-0.417554</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.517519</v>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>-0.7810049999999999</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-1.089397</v>
+        <v>-1.606916</v>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
@@ -3816,7 +3816,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3984,7 +3988,11 @@
           <t>Prepaid and deposits 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4310,7 +4318,11 @@
           <t>Prepaid and deposits 5</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.00615</v>
       </c>
@@ -4530,7 +4542,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -4886,7 +4902,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -8820,10 +8840,10 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0.779196</v>
+        <v>-0.779196</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>2.713756</v>
+        <v>-2.713756</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BECN.xlsx
+++ b/output/pdf_financials_xlsx/BECN.xlsx
@@ -611,10 +611,10 @@
         <v>0.883432</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.284348</v>
+        <v>2.361573</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.90032</v>
+        <v>3.315545</v>
       </c>
     </row>
     <row r="11">
@@ -1084,7 +1084,7 @@
         <v>1.287295</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.22623</v>
       </c>
     </row>
     <row r="35">
@@ -1122,7 +1122,7 @@
         <v>1.287295</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.22623</v>
       </c>
     </row>
     <row r="37">
@@ -1350,7 +1350,7 @@
         <v>1.07981</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.449854</v>
+        <v>1.223624</v>
       </c>
     </row>
     <row r="49">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">

--- a/output/pdf_financials_xlsx/BECN.xlsx
+++ b/output/pdf_financials_xlsx/BECN.xlsx
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.045249</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.134567</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.115816</v>
       </c>
     </row>
     <row r="29">
@@ -987,13 +987,13 @@
         <v>-0.779196</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.713756</v>
+        <v>-2.668507</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.451154</v>
+        <v>-0.316587</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.281917</v>
+        <v>-2.166101</v>
       </c>
     </row>
     <row r="30">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-10.43020184220954</v>
+        <v>-7.319155566878697</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-77.79669164524509</v>
+        <v>-73.84821252019992</v>
       </c>
     </row>
     <row r="31">
@@ -2338,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.045249</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.134567</v>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
@@ -4654,7 +4654,11 @@
           <t>Depreciation property and equipment 8</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -4688,7 +4692,11 @@
           <t>Depreciation of right-of-use asset 11</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -6498,7 +6506,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -6530,7 +6542,11 @@
           <t>Depreciation of right-of-use asset 11</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BECN.xlsx
+++ b/output/pdf_financials_xlsx/BECN.xlsx
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.019559</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.050328</v>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
@@ -4766,7 +4766,11 @@
           <t>Interest and accretion expense 9,10,11,17</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -5748,7 +5752,11 @@
           <t>Interest and accretion expense 7,8</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6190,7 +6198,11 @@
           <t>Fair value of warrants issued on private placement $</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
